--- a/SNTL_UIList.xlsx
+++ b/SNTL_UIList.xlsx
@@ -57,7 +57,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -124,6 +124,11 @@
         <fgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAE8FC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -151,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,6 +224,12 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,6 +244,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -603,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1274,176 +1286,180 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>SCR-020</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>오더 목록</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>오더관리</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>오더 기본관리</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>회원/운영자</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>오더 검색, 목록, 상태 필터, 페이징</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>/api/orders</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>선불금 관리</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>선불금 관리</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>개인회원/법인관리자</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>잔액 조회, 충전·환불 요청 이력, 버튼 이동</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>/api/prepaid/balance</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>SCR-021, SCR-022</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>SCR-016, SCR-017</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>개인/법인 공통 화면</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>SCR-021</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>오더 등록</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>오더관리</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>오더 기본관리</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>회원</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>송하인/수하인/화물정보 입력</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>/api/orders</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="n">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SCR-016</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>선불금 충전 요청</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>선불금 관리</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>개인회원/법인관리자</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>충전 금액·입금자명·입금 예정일 입력, 요청 제출</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>/api/prepaid/charge</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>SCR-020, SCR-023</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>오더번호 자동생성</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>입금 계좌 안내 표시</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>SCR-022</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>오더 상세/수정</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>오더관리</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>오더 기본관리</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>회원/운영자</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>오더 상세 조회, 수정, 삭제</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>/api/orders/{id}</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="n">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>SCR-017</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>선불금 환불 요청</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>회원관리</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>선불금 관리</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>개인회원/법인관리자</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>환불 금액·계좌 정보 입력, 잔액 검증 후 요청</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>/api/prepaid/refund</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>SCR-020</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>입고 후 수정불가</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>SCR-015</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>잔액 부족 시 요청 불가</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -1452,12 +1468,12 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>SCR-023</t>
+          <t>SCR-020</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>서비스 추가</t>
+          <t>오더 목록</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1467,22 +1483,22 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>서비스 관리</t>
+          <t>오더 기본관리</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>회원</t>
+          <t>회원/운영자</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>AIR/SEA/CIR/CCL 서비스 선택 및 정보 입력</t>
+          <t>오더 검색, 목록, 상태 필터, 페이징</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>/api/orders/{id}/services</t>
+          <t>/api/orders</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
@@ -1490,14 +1506,10 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>SCR-022</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>서비스별 입력항목 상이</t>
-        </is>
-      </c>
+          <t>SCR-021, SCR-022</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1512,566 +1524,578 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>SCR-021</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>오더 등록</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>오더관리</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>오더 기본관리</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>송하인/수하인/화물정보 입력</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>/api/orders</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>SCR-020, SCR-023</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>오더번호 자동생성</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>오더 상세/수정</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>오더관리</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>오더 기본관리</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>회원/운영자</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>오더 상세 조회, 수정, 삭제</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>/api/orders/{id}</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>SCR-020</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>입고 후 수정불가</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>SCR-023</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>서비스 추가</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>오더관리</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>서비스 관리</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>AIR/SEA/CIR/CCL 서비스 선택 및 정보 입력</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>/api/orders/{id}/services</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>SCR-022</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>서비스별 입력항목 상이</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>SCR-024</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>운송비용 조회</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>오더관리</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>운송비용 관리</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>회원/운영자</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>자동계산 운송비, Extra Charge 입력</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>/api/orders/{id}/costs</t>
         </is>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>SCR-022</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>비용 계산식 적용</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>SCR-030</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>마스터오더 목록</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>마스터오더관리</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>마스터오더 조회</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>마스터오더 검색, 목록, 상태 필터</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>/api/master-orders</t>
         </is>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>SCR-031, SCR-032</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>SCR-031</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>마스터오더 등록/패킹</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>마스터오더관리</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>마스터오더 등록</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>마스터오더 생성, 오더 패킹(추가/제거)</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>/api/master-orders</t>
         </is>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>SCR-030</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>SCR-032</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>마스터오더 상세</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>마스터오더관리</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>마스터오더 조회</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>포함 오더 목록, 서비스 정보, Tracking 현황</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>/api/master-orders/{id}</t>
         </is>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>SCR-030</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>SCR-040</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>창고 입고 처리</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>창고관리</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>입고 관리</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>바코드 스캔, 입고 확인 및 처리</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>/api/warehouse/receipt</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H24" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>SCR-041</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>입고 후 오더 수정불가</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>SCR-041</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>창고 출고 처리</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>창고관리</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>출고 관리</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>바코드 스캔, 운송장 출력, 출고 처리</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>/api/warehouse/release</t>
         </is>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H25" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>SCR-040</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>운송장 PDF 출력</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>SCR-042</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>창고 현황</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>창고관리</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>입고 관리</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>입고 현황 조회, 재고 목록</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>/api/warehouse/status</t>
         </is>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H26" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="12" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>SCR-050</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>AIR Tracking</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>운송Tracking</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>항운(AIR) Tracking</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>회원/운영자</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>항공 화물 실시간 추적, 스케줄 조회</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>/api/tracking/air/{id}</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr"/>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>외부 AIR API 연동</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>SCR-051</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>SEA Tracking</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>운송Tracking</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>해운(SEA) Tracking</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>회원/운영자</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>선박 운송 현황 추적, 선적 스케줄</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>/api/tracking/sea/{id}</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>외부 SEA API 연동</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>SCR-052</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>CIR Tracking</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>운송Tracking</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>택배(CIR) Tracking</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>회원/운영자</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>국제택배 실시간 추적</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>/api/tracking/cir/{id}</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr"/>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>외부 택배사 API 연동</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -2080,12 +2104,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>SCR-053</t>
+          <t>SCR-050</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>통관신고 현황</t>
+          <t>AIR Tracking</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2095,7 +2119,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>통관신고 관리</t>
+          <t>항운(AIR) Tracking</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2105,12 +2129,12 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>통관 신고 현황, 세관 응답 조회</t>
+          <t>항공 화물 실시간 추적, 스케줄 조회</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>/api/customs/{id}</t>
+          <t>/api/tracking/air/{id}</t>
         </is>
       </c>
       <c r="H27" s="13" t="n">
@@ -2119,183 +2143,183 @@
       <c r="I27" s="14" t="inlineStr"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
+          <t>외부 AIR API 연동</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>SCR-051</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>SEA Tracking</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>운송Tracking</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>해운(SEA) Tracking</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>회원/운영자</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>선박 운송 현황 추적, 선적 스케줄</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>/api/tracking/sea/{id}</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>외부 SEA API 연동</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>SCR-052</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>CIR Tracking</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>운송Tracking</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>택배(CIR) Tracking</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>회원/운영자</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>국제택배 실시간 추적</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>/api/tracking/cir/{id}</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>외부 택배사 API 연동</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>SCR-053</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>통관신고 현황</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>운송Tracking</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>통관신고 관리</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>회원/운영자</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>통관 신고 현황, 세관 응답 조회</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>/api/customs/{id}</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr"/>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
           <t>CCL 서비스 연계</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>SCR-060</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>청구서 목록</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>회계/청구</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>청구서 관리</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>운영자/회원</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>청구서 목록, 검색, 상태 필터</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>/api/invoices</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>SCR-061</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr"/>
-      <c r="K28" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L28" s="15" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>SCR-061</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>청구서 상세</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>회계/청구</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>청구서 관리</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>운영자/회원</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>청구 항목 상세, 입금 처리</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>/api/invoices/{id}</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>SCR-060, SCR-062</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr"/>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>SCR-062</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>입금 처리</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>회계/청구</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>입금 관리</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>운영자</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>입금 확인, 미수금 처리</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>/api/invoices/{id}/payment</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>SCR-061</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
+      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -2304,12 +2328,12 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>SCR-063</t>
+          <t>SCR-060</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>세금계산서</t>
+          <t>청구서 목록</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -2319,36 +2343,36 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>세금계산서</t>
+          <t>청구서 관리</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>운영자</t>
+          <t>운영자/회원</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>세금계산서 발행, 조회, 재발행</t>
+          <t>청구서 목록, 검색, 상태 필터</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>/api/tax-invoices</t>
+          <t>/api/invoices</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>SCR-060</t>
+          <t>SCR-061</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr"/>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
@@ -2360,12 +2384,12 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>SCR-064</t>
+          <t>SCR-061</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>수입/비용 현황</t>
+          <t>청구서 상세</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -2375,36 +2399,36 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>수입 관리</t>
+          <t>청구서 관리</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>운영자/회원</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>기간별 수입, 원가, 수익 분석 차트</t>
+          <t>청구 항목 상세, 입금 처리</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>/api/statistics/revenue</t>
+          <t>/api/invoices/{id}</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr"/>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>차트 포함</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>SCR-060, SCR-062</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr"/>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L32" s="15" t="inlineStr">
@@ -2416,12 +2440,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>SCR-065</t>
+          <t>SCR-062</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>운송원가 관리</t>
+          <t>입금 처리</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -2431,28 +2455,32 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>운송원가 관리</t>
+          <t>입금 관리</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>운영자</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>서비스/구간별 원가 등록·수정</t>
+          <t>입금 확인, 미수금 처리</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>/api/transport-costs</t>
+          <t>/api/invoices/{id}/payment</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="16" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>SCR-061</t>
+        </is>
+      </c>
       <c r="J33" s="16" t="inlineStr"/>
       <c r="K33" s="15" t="inlineStr">
         <is>
@@ -2466,340 +2494,340 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>SCR-063</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>세금계산서</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>회계/청구</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>세금계산서</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>운영자</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>세금계산서 발행, 조회, 재발행</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>/api/tax-invoices</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>SCR-060</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr"/>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L34" s="15" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>SCR-064</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>수입/비용 현황</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>회계/청구</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>수입 관리</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>기간별 수입, 원가, 수익 분석 차트</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>/api/statistics/revenue</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr"/>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>차트 포함</t>
+        </is>
+      </c>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>SCR-065</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>운송원가 관리</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>회계/청구</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>운송원가 관리</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>서비스/구간별 원가 등록·수정</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>/api/transport-costs</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr"/>
+      <c r="J36" s="16" t="inlineStr"/>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L36" s="15" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>SCR-070</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>VOC 목록</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>VOC관리</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>VOC 조회</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>회원/운영자</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>VOC 목록, 상태 필터, 처리현황</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>/api/voc</t>
         </is>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H37" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>SCR-071, SCR-072</t>
         </is>
       </c>
-      <c r="J34" s="18" t="inlineStr"/>
-      <c r="K34" s="17" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr"/>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L34" s="17" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>SCR-071</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>VOC 등록</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>VOC관리</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>VOC 등록</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>오더 선택, 불만/문의 내용 등록</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>/api/voc</t>
         </is>
       </c>
-      <c r="H35" s="17" t="n">
+      <c r="H38" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>SCR-070</t>
         </is>
       </c>
-      <c r="J35" s="18" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>알림 자동 발송</t>
         </is>
       </c>
-      <c r="K35" s="17" t="inlineStr">
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L35" s="17" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>SCR-072</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>VOC 답변</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>VOC관리</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>VOC 답변</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>VOC 내용 조회, 답변 등록, 상태 변경</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>/api/voc/{id}/reply</t>
         </is>
       </c>
-      <c r="H36" s="17" t="n">
+      <c r="H39" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>SCR-070</t>
         </is>
       </c>
-      <c r="J36" s="18" t="inlineStr">
+      <c r="J39" s="18" t="inlineStr">
         <is>
           <t>고객 알림 발송</t>
         </is>
       </c>
-      <c r="K36" s="17" t="inlineStr">
+      <c r="K39" s="17" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>SCR-080</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>QnA 목록/등록</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>고객지원</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>QnA</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>회원</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>1:1 문의 목록, 문의 등록</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>/api/support/qna</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="20" t="inlineStr">
-        <is>
-          <t>SCR-081</t>
-        </is>
-      </c>
-      <c r="J37" s="20" t="inlineStr"/>
-      <c r="K37" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L37" s="19" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>SCR-081</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>QnA 답변</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>고객지원</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>QnA</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>운영자</t>
-        </is>
-      </c>
-      <c r="F38" s="20" t="inlineStr">
-        <is>
-          <t>관리자 답변 등록, 처리상태 변경</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>/api/support/qna/{id}</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
-        <is>
-          <t>SCR-080</t>
-        </is>
-      </c>
-      <c r="J38" s="20" t="inlineStr"/>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>SCR-082</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>고객지원</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>FAQ 카테고리별 조회, 관리자 CRUD</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>/api/support/faq</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="20" t="inlineStr"/>
-      <c r="J39" s="20" t="inlineStr"/>
-      <c r="K39" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L39" s="19" t="inlineStr">
+      <c r="L39" s="17" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -2808,12 +2836,12 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>SCR-083</t>
+          <t>SCR-080</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>QnA 목록/등록</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
@@ -2823,207 +2851,203 @@
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>QnA</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>회원</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>공지사항 목록, 상세, 중요공지 상단고정</t>
+          <t>1:1 문의 목록, 문의 등록</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>/api/support/notice</t>
+          <t>/api/support/qna</t>
         </is>
       </c>
       <c r="H40" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="20" t="inlineStr"/>
-      <c r="J40" s="20" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>SCR-081</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr"/>
+      <c r="K40" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>SCR-081</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>QnA 답변</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>고객지원</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>QnA</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>운영자</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>관리자 답변 등록, 처리상태 변경</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>/api/support/qna/{id}</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>SCR-080</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr"/>
+      <c r="K41" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>SCR-082</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>고객지원</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>FAQ 카테고리별 조회, 관리자 CRUD</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>/api/support/faq</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="20" t="inlineStr"/>
+      <c r="J42" s="20" t="inlineStr"/>
+      <c r="K42" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>SCR-083</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>고객지원</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>공지사항 목록, 상세, 중요공지 상단고정</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>/api/support/notice</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="20" t="inlineStr"/>
+      <c r="J43" s="20" t="inlineStr">
         <is>
           <t>관리자: CRUD</t>
         </is>
       </c>
-      <c r="K40" s="19" t="inlineStr">
+      <c r="K43" s="19" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>SCR-090</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>관리자 대시보드</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>통계 관리</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="F41" s="22" t="inlineStr">
-        <is>
-          <t>오더현황, 수익, 회원통계 요약 KPI+차트</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>/api/admin/dashboard</t>
-        </is>
-      </c>
-      <c r="H41" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="22" t="inlineStr"/>
-      <c r="J41" s="22" t="inlineStr"/>
-      <c r="K41" s="21" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="L41" s="21" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>SCR-091</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>회원 목록/관리</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>회원 검색, 상세, 등급/상태 변경</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr">
-        <is>
-          <t>/api/admin/members</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="22" t="inlineStr">
-        <is>
-          <t>SCR-092</t>
-        </is>
-      </c>
-      <c r="J42" s="22" t="inlineStr"/>
-      <c r="K42" s="21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>미개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="21" t="inlineStr">
-        <is>
-          <t>SCR-092</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>법인 심사</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>회원관리</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="F43" s="22" t="inlineStr">
-        <is>
-          <t>법인 가입 신청, 첨부파일 확인, 승인/거부</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="inlineStr">
-        <is>
-          <t>/api/admin/corporate/review</t>
-        </is>
-      </c>
-      <c r="H43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="22" t="inlineStr">
-        <is>
-          <t>SCR-091</t>
-        </is>
-      </c>
-      <c r="J43" s="22" t="inlineStr">
-        <is>
-          <t>승인 시 알림 발송</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L43" s="21" t="inlineStr">
+      <c r="L43" s="19" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -3032,12 +3056,12 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>SCR-093</t>
+          <t>SCR-090</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>메뉴 관리</t>
+          <t>관리자 대시보드</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
@@ -3047,7 +3071,7 @@
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>메뉴 관리</t>
+          <t>통계 관리</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -3057,23 +3081,19 @@
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t>메뉴 트리 조회, 등록, 수정, 순서변경</t>
+          <t>오더현황, 수익, 회원통계 요약 KPI+차트</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>/api/system/menus</t>
+          <t>/api/admin/dashboard</t>
         </is>
       </c>
       <c r="H44" s="21" t="n">
         <v>2</v>
       </c>
       <c r="I44" s="22" t="inlineStr"/>
-      <c r="J44" s="22" t="inlineStr">
-        <is>
-          <t>계층형 트리</t>
-        </is>
-      </c>
+      <c r="J44" s="22" t="inlineStr"/>
       <c r="K44" s="21" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3088,12 +3108,12 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>SCR-094</t>
+          <t>SCR-091</t>
         </is>
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>코드 관리</t>
+          <t>회원 목록/관리</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
@@ -3103,7 +3123,7 @@
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>코드 관리</t>
+          <t>회원관리</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
@@ -3113,22 +3133,26 @@
       </c>
       <c r="F45" s="22" t="inlineStr">
         <is>
-          <t>코드그룹 및 공통코드 CRUD</t>
+          <t>회원 검색, 상세, 등급/상태 변경</t>
         </is>
       </c>
       <c r="G45" s="22" t="inlineStr">
         <is>
-          <t>/api/system/codes</t>
+          <t>/api/admin/members</t>
         </is>
       </c>
       <c r="H45" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>SCR-092</t>
+        </is>
+      </c>
       <c r="J45" s="22" t="inlineStr"/>
       <c r="K45" s="21" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L45" s="21" t="inlineStr">
@@ -3140,12 +3164,12 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="21" t="inlineStr">
         <is>
-          <t>SCR-095</t>
+          <t>SCR-092</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>권한 관리</t>
+          <t>법인 심사</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
@@ -3155,7 +3179,7 @@
       </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>권한 관리</t>
+          <t>회원관리</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
@@ -3165,26 +3189,30 @@
       </c>
       <c r="F46" s="22" t="inlineStr">
         <is>
-          <t>역할 정의, 메뉴별 접근권한 설정</t>
+          <t>법인 가입 신청, 첨부파일 확인, 승인/거부</t>
         </is>
       </c>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>/api/system/roles</t>
+          <t>/api/admin/corporate/review</t>
         </is>
       </c>
       <c r="H46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>SCR-091</t>
+        </is>
+      </c>
       <c r="J46" s="22" t="inlineStr">
         <is>
-          <t>Role 기반 접근제어</t>
+          <t>승인 시 알림 발송</t>
         </is>
       </c>
       <c r="K46" s="21" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L46" s="21" t="inlineStr">
@@ -3196,12 +3224,12 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>SCR-096</t>
+          <t>SCR-093</t>
         </is>
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>택배사 관리</t>
+          <t>메뉴 관리</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
@@ -3211,7 +3239,7 @@
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>택배사 관리</t>
+          <t>메뉴 관리</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
@@ -3221,19 +3249,23 @@
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>택배사 CRUD, Tracking URL 관리</t>
+          <t>메뉴 트리 조회, 등록, 수정, 순서변경</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
         <is>
-          <t>/api/system/couriers</t>
+          <t>/api/system/menus</t>
         </is>
       </c>
       <c r="H47" s="21" t="n">
         <v>2</v>
       </c>
       <c r="I47" s="22" t="inlineStr"/>
-      <c r="J47" s="22" t="inlineStr"/>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>계층형 트리</t>
+        </is>
+      </c>
       <c r="K47" s="21" t="inlineStr">
         <is>
           <t>P2</t>
@@ -3248,12 +3280,12 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="21" t="inlineStr">
         <is>
-          <t>SCR-097</t>
+          <t>SCR-094</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>알림 관리</t>
+          <t>코드 관리</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
@@ -3263,7 +3295,7 @@
       </c>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>알림 관리</t>
+          <t>코드 관리</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
@@ -3273,12 +3305,12 @@
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t>알림 발송 내역, 공지 알림 생성</t>
+          <t>코드그룹 및 공통코드 CRUD</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>/api/notifications</t>
+          <t>/api/system/codes</t>
         </is>
       </c>
       <c r="H48" s="21" t="n">
@@ -3300,12 +3332,12 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>SCR-098</t>
+          <t>SCR-095</t>
         </is>
       </c>
       <c r="B49" s="22" t="inlineStr">
         <is>
-          <t>통계</t>
+          <t>권한 관리</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
@@ -3315,7 +3347,7 @@
       </c>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>통계 관리</t>
+          <t>권한 관리</t>
         </is>
       </c>
       <c r="E49" s="21" t="inlineStr">
@@ -3325,26 +3357,26 @@
       </c>
       <c r="F49" s="22" t="inlineStr">
         <is>
-          <t>운송/비용 기간별 통계, 차트</t>
+          <t>역할 정의, 메뉴별 접근권한 설정</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>/api/statistics</t>
+          <t>/api/system/roles</t>
         </is>
       </c>
       <c r="H49" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="22" t="inlineStr"/>
       <c r="J49" s="22" t="inlineStr">
         <is>
-          <t>차트</t>
+          <t>Role 기반 접근제어</t>
         </is>
       </c>
       <c r="K49" s="21" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L49" s="21" t="inlineStr">
@@ -3356,12 +3388,12 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="21" t="inlineStr">
         <is>
-          <t>SCR-099</t>
+          <t>SCR-096</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>데이터 백업</t>
+          <t>택배사 관리</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
@@ -3371,7 +3403,7 @@
       </c>
       <c r="D50" s="21" t="inlineStr">
         <is>
-          <t>데이터 관리</t>
+          <t>택배사 관리</t>
         </is>
       </c>
       <c r="E50" s="21" t="inlineStr">
@@ -3381,25 +3413,581 @@
       </c>
       <c r="F50" s="22" t="inlineStr">
         <is>
-          <t>DB 백업 실행, 백업 이력 조회</t>
+          <t>택배사 CRUD, Tracking URL 관리</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>/api/admin/backup</t>
+          <t>/api/system/couriers</t>
         </is>
       </c>
       <c r="H50" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" s="22" t="inlineStr"/>
       <c r="J50" s="22" t="inlineStr"/>
       <c r="K50" s="21" t="inlineStr">
         <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L50" s="21" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>SCR-097</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>알림 관리</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>알림 관리</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>알림 발송 내역, 공지 알림 생성</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>/api/notifications</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="22" t="inlineStr"/>
+      <c r="J51" s="22" t="inlineStr"/>
+      <c r="K51" s="21" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L51" s="21" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>SCR-098</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>통계</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>통계 관리</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>운송/비용 기간별 통계, 차트</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>/api/statistics</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" s="22" t="inlineStr"/>
+      <c r="J52" s="22" t="inlineStr">
+        <is>
+          <t>차트</t>
+        </is>
+      </c>
+      <c r="K52" s="21" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="L50" s="21" t="inlineStr">
+      <c r="L52" s="21" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>SCR-099</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>데이터 백업</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>데이터 관리</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>DB 백업 실행, 백업 이력 조회</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>/api/admin/backup</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="22" t="inlineStr"/>
+      <c r="J53" s="22" t="inlineStr"/>
+      <c r="K53" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>SCR-100</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>선불금 요청 관리</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>선불금 관리</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>충전/환불 요청 목록 조회, PENDING 요청 확인·거부 처리</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>/api/prepaid/admin</t>
+        </is>
+      </c>
+      <c r="H54" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="24" t="inlineStr"/>
+      <c r="J54" s="24" t="inlineStr">
+        <is>
+          <t>확인 시 회원 잔액 자동 반영</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L54" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>SCR-101</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>운임요율 관리</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>운임요율 관리</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>개인등급별(BASIC/SILVER/GOLD/VIP) 및 법인별 운임요율 CRUD, 적용기간 설정</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>/api/fare-rates</t>
+        </is>
+      </c>
+      <c r="H55" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="24" t="inlineStr"/>
+      <c r="J55" s="24" t="inlineStr">
+        <is>
+          <t>서비스구분(AIR/SEA/CIR/CCL) 탭</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L55" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>SCR-102</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>환율 관리</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>환율 관리</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>최신 환율 목록 조회, 서울외국환중개소 API 수동 연계, 환율 수동 수정</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>/api/exchange-rates</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="24" t="inlineStr"/>
+      <c r="J56" s="24" t="inlineStr">
+        <is>
+          <t>영업일 자동 연계 이력 포함</t>
+        </is>
+      </c>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>SCR-103</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>항공운송수단 관리</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>항공 운송수단</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>항공 운송구간(출발/도착 국가·공항) CRUD, 구간별 부피·중량기준 운송원가 CRUD</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>/api/air-transports</t>
+        </is>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="24" t="inlineStr"/>
+      <c r="J57" s="24" t="inlineStr">
+        <is>
+          <t>편명·원가 탭 분리</t>
+        </is>
+      </c>
+      <c r="K57" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L57" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>SCR-104</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>해운운송수단 관리</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>해운 운송수단</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>해운 운송구간(출발/도착 국가·항구) CRUD, 구간별 부피·중량기준 운송원가 CRUD</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>/api/sea-transports</t>
+        </is>
+      </c>
+      <c r="H58" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="24" t="inlineStr"/>
+      <c r="J58" s="24" t="inlineStr">
+        <is>
+          <t>선사명·원가 탭 분리</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L58" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>SCR-105</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>통관사 관리</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>통관사 관리</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>통관사 CRUD(국가·서비스구분·API연동ON/OFF), 통관원가 CRUD</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>/api/customs-brokers</t>
+        </is>
+      </c>
+      <c r="H59" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="24" t="inlineStr"/>
+      <c r="J59" s="24" t="inlineStr">
+        <is>
+          <t>API연동구분 ON/OFF 토글</t>
+        </is>
+      </c>
+      <c r="K59" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L59" s="23" t="inlineStr">
+        <is>
+          <t>미개발</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>SCR-106</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>택배배송장 관리</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
+        <is>
+          <t>택배배송장 관리</t>
+        </is>
+      </c>
+      <c r="E60" s="23" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>택배사별·국가별 배송장 양식 파일 업로드·다운로드·삭제</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>/api/courier-waybills</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>SCR-096</t>
+        </is>
+      </c>
+      <c r="J60" s="24" t="inlineStr">
+        <is>
+          <t>MinIO 파일 저장</t>
+        </is>
+      </c>
+      <c r="K60" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L60" s="23" t="inlineStr">
         <is>
           <t>미개발</t>
         </is>
@@ -3419,7 +4007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3427,7 +4015,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>UI 화면 수 요약</t>
         </is>
@@ -3448,154 +4036,164 @@
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>로그인/인증</t>
         </is>
       </c>
-      <c r="B3" s="25" t="n">
+      <c r="B3" s="27" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>회원관리</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>오더관리</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>오더관리</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>5</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>마스터오더관리</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="27" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>창고관리</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="27" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>운송Tracking</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="27" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>회계/청구</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="27" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>VOC관리</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="27" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>고객지원</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="27" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="27" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>기초정보관리</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B14" s="39" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>화면 수</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="B17" s="27" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B18" s="27" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B19" s="27" t="n">
         <v>4</v>
       </c>
     </row>
